--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-additional-when-codes.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-additional-when-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T16:12:39+00:00</t>
+    <t>2026-07-20T14:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-additional-when-codes.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-additional-when-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:23:22+00:00</t>
+    <t>2026-08-12T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-additional-when-codes.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-additional-when-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T15:16:17+00:00</t>
+    <t>2026-08-13T08:08:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-additional-when-codes.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-additional-when-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:08:00+00:00</t>
+    <t>2026-08-13T08:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-additional-when-codes.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-additional-when-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:33:40+00:00</t>
+    <t>2026-08-13T08:58:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-additional-when-codes.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-additional-when-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:58:16+00:00</t>
+    <t>2026-08-13T09:15:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-additional-when-codes.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-additional-when-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:15:12+00:00</t>
+    <t>2026-08-13T09:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-additional-when-codes.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-additional-when-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:41:50+00:00</t>
+    <t>2026-08-13T12:00:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-additional-when-codes.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-additional-when-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T12:00:16+00:00</t>
+    <t>2026-08-13T12:31:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
